--- a/Sentiment_RTM.xlsx
+++ b/Sentiment_RTM.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7e632153490cda6a/Documents/Strath/Masters/sentiment-analysis-tool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_2B59D2BFD310585BAAF465B3446430B34019EB13" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD1BB486-8786-4A02-AF85-0E90B7BBB6C1}"/>
+  <xr:revisionPtr revIDLastSave="111" documentId="11_2B59D2BFD310585BAAF465B3446430B34019EB13" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32D66417-4AFB-4D02-A567-358F41C84EC2}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="111">
   <si>
     <t>Req ID</t>
   </si>
@@ -43,9 +44,6 @@
     <t>Test ingestion from multiple sources</t>
   </si>
   <si>
-    <t>Covered</t>
-  </si>
-  <si>
     <t>FRQ2</t>
   </si>
   <si>
@@ -154,9 +152,6 @@
     <t>Test model on labeled dataset</t>
   </si>
   <si>
-    <t>Pending</t>
-  </si>
-  <si>
     <t>NFRQ2</t>
   </si>
   <si>
@@ -260,13 +255,112 @@
   </si>
   <si>
     <t>Status</t>
+  </si>
+  <si>
+    <t>Requirement Type</t>
+  </si>
+  <si>
+    <t>Functional</t>
+  </si>
+  <si>
+    <t>Non-functional</t>
+  </si>
+  <si>
+    <t>Test Case ID</t>
+  </si>
+  <si>
+    <t>TC001</t>
+  </si>
+  <si>
+    <t>TC002</t>
+  </si>
+  <si>
+    <t>TC003</t>
+  </si>
+  <si>
+    <t>TC004</t>
+  </si>
+  <si>
+    <t>TC005</t>
+  </si>
+  <si>
+    <t>TC006</t>
+  </si>
+  <si>
+    <t>TC007</t>
+  </si>
+  <si>
+    <t>TC008</t>
+  </si>
+  <si>
+    <t>TC009</t>
+  </si>
+  <si>
+    <t>TC010</t>
+  </si>
+  <si>
+    <t>TC011</t>
+  </si>
+  <si>
+    <t>TC012</t>
+  </si>
+  <si>
+    <t>TC013</t>
+  </si>
+  <si>
+    <t>TC014</t>
+  </si>
+  <si>
+    <t>TC015</t>
+  </si>
+  <si>
+    <t>TC016</t>
+  </si>
+  <si>
+    <t>TC017</t>
+  </si>
+  <si>
+    <t>TC018</t>
+  </si>
+  <si>
+    <t>TC019</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>Project Name: Research Thesis</t>
+  </si>
+  <si>
+    <t>Project Description: Sentiment Analysis Tool For the Kenyan Banking Sector</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Tool Used</t>
+  </si>
+  <si>
+    <t>Streamlit</t>
+  </si>
+  <si>
+    <t>Postman</t>
+  </si>
+  <si>
+    <t>unittest</t>
+  </si>
+  <si>
+    <t>Postgres</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -279,8 +373,28 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -288,19 +402,43 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
+      <gradientFill degree="90">
+        <stop position="0">
+          <color theme="0"/>
+        </stop>
+        <stop position="1">
+          <color theme="0" tint="-5.0965910824915313E-2"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor rgb="FFFFEB9C"/>
-      </patternFill>
+      <gradientFill degree="90">
+        <stop position="0">
+          <color rgb="FF00B050"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FF00B050"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill degree="90">
+        <stop position="0">
+          <color rgb="FFFF0000"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFFF0000"/>
+        </stop>
+      </gradientFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -323,22 +461,136 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -349,6 +601,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -636,357 +892,617 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.26953125" customWidth="1"/>
-    <col min="3" max="3" width="26.08984375" customWidth="1"/>
-    <col min="4" max="4" width="30.36328125" customWidth="1"/>
-    <col min="5" max="5" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.6328125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" customWidth="1"/>
+    <col min="4" max="4" width="19.90625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.90625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.1796875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="7.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="19"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" s="19"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="19"/>
+    </row>
+    <row r="5" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A5" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B5" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C5" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="D5" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="E5" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="G5" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="D6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E6" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="G6" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" t="s">
+        <v>109</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" t="s">
+        <v>109</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G16" s="3"/>
+      <c r="H16" s="7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G17" s="3"/>
+      <c r="H17" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G18" s="3"/>
+      <c r="H18" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G19" s="3"/>
+      <c r="H19" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G20" s="3"/>
+      <c r="H20" s="7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G21" s="3"/>
+      <c r="H21" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A22" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G22" s="3"/>
+      <c r="H22" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G23" s="3"/>
+      <c r="H23" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A24" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="G24" s="9"/>
+      <c r="H24" s="13" t="s">
+        <v>101</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <conditionalFormatting sqref="H6:H24">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{136F95D5-979B-4567-AE84-7D33BC75EF98}">
+          <x14:formula1>
+            <xm:f>Sheet2!$A$1:$A$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>H1:H1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A538EBC-4599-4654-B0D3-1A6B2B3C60B8}">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" s="16" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" s="17" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" t="s">
-        <v>41</v>
-      </c>
-      <c r="C11" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" t="s">
-        <v>43</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>45</v>
-      </c>
-      <c r="B12" t="s">
-        <v>46</v>
-      </c>
-      <c r="C12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" t="s">
-        <v>47</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>48</v>
-      </c>
-      <c r="B13" t="s">
-        <v>49</v>
-      </c>
-      <c r="C13" t="s">
-        <v>50</v>
-      </c>
-      <c r="D13" t="s">
-        <v>51</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>52</v>
-      </c>
-      <c r="B14" t="s">
-        <v>53</v>
-      </c>
-      <c r="C14" t="s">
-        <v>54</v>
-      </c>
-      <c r="D14" t="s">
-        <v>55</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>56</v>
-      </c>
-      <c r="B15" t="s">
-        <v>57</v>
-      </c>
-      <c r="C15" t="s">
-        <v>58</v>
-      </c>
-      <c r="D15" t="s">
-        <v>59</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>60</v>
-      </c>
-      <c r="B16" t="s">
-        <v>61</v>
-      </c>
-      <c r="C16" t="s">
-        <v>62</v>
-      </c>
-      <c r="D16" t="s">
-        <v>63</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>64</v>
-      </c>
-      <c r="B17" t="s">
-        <v>65</v>
-      </c>
-      <c r="C17" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17" t="s">
-        <v>66</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>67</v>
-      </c>
-      <c r="B18" t="s">
-        <v>68</v>
-      </c>
-      <c r="C18" t="s">
-        <v>42</v>
-      </c>
-      <c r="D18" t="s">
-        <v>69</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>70</v>
-      </c>
-      <c r="B19" t="s">
-        <v>71</v>
-      </c>
-      <c r="C19" t="s">
-        <v>72</v>
-      </c>
-      <c r="D19" t="s">
-        <v>73</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>74</v>
-      </c>
-      <c r="B20" t="s">
-        <v>75</v>
-      </c>
-      <c r="C20" t="s">
-        <v>76</v>
-      </c>
-      <c r="D20" t="s">
-        <v>77</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>7</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>